--- a/web/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/web/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1825,7 +1825,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>第19号屋</t>
+          <t>第20号屋</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2476</v>
+        <v>2500</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>第20号屋</t>
+          <t>第21号屋</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1914,11 +1914,11 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2500</v>
+        <v>3343</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1958,14 +1958,14 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>第21号屋</t>
+          <t>第22号屋</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1984,11 +1984,11 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3343</v>
+        <v>3302</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2028,14 +2028,14 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>第22号屋</t>
+          <t>第23号屋</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2098,14 +2098,14 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>第23号屋</t>
+          <t>第25号屋</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2128,23 +2128,19 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2021-03-05</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>125328000</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>37955</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2153,12 +2149,12 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2168,14 +2164,14 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>第25号屋</t>
+          <t>第26号屋</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2198,19 +2194,23 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>125328000</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>37955</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>第26号屋</t>
+          <t>第27号屋</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2311,7 +2311,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>第27号屋</t>
+          <t>第28号屋</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2381,7 +2381,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>第28号屋</t>
+          <t>第29号屋</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2444,14 +2444,14 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>第29号屋</t>
+          <t>第30号屋</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2470,27 +2470,23 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3302</v>
+        <v>3337</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2000-08-16</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>57000000</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>17081</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2499,12 +2495,12 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -2514,14 +2510,14 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>第30号屋</t>
+          <t>第31号屋</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2540,23 +2536,27 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3337</v>
+        <v>3343</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2000-08-16</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>57000000</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>17081</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>第31号屋</t>
+          <t>第32号屋</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3343</v>
+        <v>3302</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>第32号屋</t>
+          <t>第33号屋</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2727,7 +2727,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>第33号屋</t>
+          <t>第35号屋</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2797,7 +2797,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>第35号屋</t>
+          <t>第36号屋</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2867,7 +2867,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>第36号屋</t>
+          <t>第37号屋</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2937,7 +2937,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>第37号屋</t>
+          <t>第38号屋</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3302</v>
+        <v>3337</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2999,76 +2999,6 @@
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>第38号屋</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>3337</v>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3143,7 +3073,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>34 套</t>
+          <t>33 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -3168,7 +3098,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>26 套</t>
+          <t>25 套</t>
         </is>
       </c>
     </row>
@@ -3375,15 +3305,6 @@
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>第19号屋
-2476呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
           <t>第20号屋
 2500呎 (4+房)
 (待售)
@@ -3391,14 +3312,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>第 4 行</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>第21号屋
 3343呎 (4+房)
@@ -3407,7 +3321,14 @@
 -</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>第 4 行</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>第22号屋
 3302呎 (4+房)
@@ -3416,7 +3337,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>第23号屋
 3302呎 (4+房)
@@ -3425,7 +3346,7 @@
 -</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>第25号屋
 3302呎 (4+房)
@@ -3434,7 +3355,7 @@
 $37,955/呎</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>第26号屋
 3302呎 (4+房)
@@ -3443,7 +3364,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>第27号屋
 3302呎 (4+房)
@@ -3452,14 +3373,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>第 5 行</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>第28号屋
 3302呎 (4+房)
@@ -3468,7 +3382,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>第29号屋
 3302呎 (4+房)
@@ -3477,7 +3398,7 @@
 -</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>第30号屋
 3337呎 (4+房)
@@ -3486,7 +3407,7 @@
 $17,081/呎</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>第31号屋
 3343呎 (4+房)
@@ -3495,7 +3416,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>第32号屋
 3302呎 (4+房)
@@ -3504,7 +3425,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>第33号屋
 3302呎 (4+房)
@@ -3513,14 +3434,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>第 6 行</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>第35号屋
 3302呎 (4+房)
@@ -3529,7 +3443,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>第36号屋
 3302呎 (4+房)
@@ -3538,7 +3459,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>第37号屋
 3302呎 (4+房)
@@ -3547,7 +3468,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>第38号屋
 3337呎 (4+房)
@@ -3556,6 +3477,7 @@
 暂无呎价</t>
         </is>
       </c>
+      <c r="E11" s="19" t="inlineStr"/>
       <c r="F11" s="19" t="inlineStr"/>
       <c r="G11" s="19" t="inlineStr"/>
     </row>

--- a/web/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/web/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -1755,7 +1755,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>第18号屋</t>
+          <t>第19号屋</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>第18号屋
+          <t>第19号屋
 2476呎 (4+房)
 (待售)
 暂无价格

--- a/web/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/web/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1755,7 +1755,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>第19号屋</t>
+          <t>第18号屋</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1825,7 +1825,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>第20号屋</t>
+          <t>第19号屋</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2500</v>
+        <v>2476</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>第21号屋</t>
+          <t>第20号屋</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1914,11 +1914,11 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3343</v>
+        <v>2500</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1958,14 +1958,14 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>第22号屋</t>
+          <t>第21号屋</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1984,11 +1984,11 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3302</v>
+        <v>3343</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2028,14 +2028,14 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>第23号屋</t>
+          <t>第22号屋</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2098,14 +2098,14 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>第25号屋</t>
+          <t>第23号屋</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2128,19 +2128,23 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2021-03-05</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>125328000</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>37955</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2149,12 +2153,12 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2164,14 +2168,14 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>第26号屋</t>
+          <t>第25号屋</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2194,23 +2198,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2021-03-05</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>125328000</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>37955</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>第27号屋</t>
+          <t>第26号屋</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2311,7 +2311,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>第28号屋</t>
+          <t>第27号屋</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2381,7 +2381,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>第29号屋</t>
+          <t>第28号屋</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2444,14 +2444,14 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>第30号屋</t>
+          <t>第29号屋</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2470,23 +2470,27 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3337</v>
+        <v>3302</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2000-08-16</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>57000000</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>17081</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2495,12 +2499,12 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -2510,14 +2514,14 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>第31号屋</t>
+          <t>第30号屋</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2536,27 +2540,23 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3343</v>
+        <v>3337</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2000-08-16</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>57000000</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>17081</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>第32号屋</t>
+          <t>第31号屋</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3302</v>
+        <v>3343</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>第33号屋</t>
+          <t>第32号屋</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2727,7 +2727,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>第35号屋</t>
+          <t>第33号屋</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2797,7 +2797,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>第36号屋</t>
+          <t>第35号屋</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2867,7 +2867,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>第37号屋</t>
+          <t>第36号屋</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2937,68 +2937,138 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
+          <t>第37号屋</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>3302</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>第38号屋</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E36" s="4" t="n">
         <v>3337</v>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>待售</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3073,7 +3143,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>33 套</t>
+          <t>34 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -3098,7 +3168,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>25 套</t>
+          <t>26 套</t>
         </is>
       </c>
     </row>
@@ -3296,6 +3366,15 @@
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
+          <t>第18号屋
+2476呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
           <t>第19号屋
 2476呎 (4+房)
 (待售)
@@ -3303,7 +3382,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>第20号屋
 2500呎 (4+房)
@@ -3312,7 +3391,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>第 4 行</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>第21号屋
 3343呎 (4+房)
@@ -3321,14 +3407,7 @@
 -</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>第 4 行</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>第22号屋
 3302呎 (4+房)
@@ -3337,7 +3416,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>第23号屋
 3302呎 (4+房)
@@ -3346,7 +3425,7 @@
 -</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>第25号屋
 3302呎 (4+房)
@@ -3355,7 +3434,7 @@
 $37,955/呎</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>第26号屋
 3302呎 (4+房)
@@ -3364,7 +3443,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>第27号屋
 3302呎 (4+房)
@@ -3373,7 +3452,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>第28号屋
 3302呎 (4+房)
@@ -3382,14 +3468,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>第 5 行</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>第29号屋
 3302呎 (4+房)
@@ -3398,7 +3477,7 @@
 -</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>第30号屋
 3337呎 (4+房)
@@ -3407,7 +3486,7 @@
 $17,081/呎</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>第31号屋
 3343呎 (4+房)
@@ -3416,7 +3495,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>第32号屋
 3302呎 (4+房)
@@ -3425,7 +3504,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>第33号屋
 3302呎 (4+房)
@@ -3434,7 +3513,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>第35号屋
 3302呎 (4+房)
@@ -3443,14 +3529,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>第 6 行</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>第36号屋
 3302呎 (4+房)
@@ -3459,7 +3538,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>第37号屋
 3302呎 (4+房)
@@ -3468,7 +3547,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>第38号屋
 3337呎 (4+房)
@@ -3477,7 +3556,6 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr"/>
       <c r="F11" s="19" t="inlineStr"/>
       <c r="G11" s="19" t="inlineStr"/>
     </row>

--- a/web/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/web/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2999,76 +2999,6 @@
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>第38号屋</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>3337</v>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3143,7 +3073,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>34 套</t>
+          <t>33 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -3168,7 +3098,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>26 套</t>
+          <t>25 套</t>
         </is>
       </c>
     </row>
@@ -3547,15 +3477,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>第38号屋
-3337呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
+      <c r="E11" s="19" t="inlineStr"/>
       <c r="F11" s="19" t="inlineStr"/>
       <c r="G11" s="19" t="inlineStr"/>
     </row>

--- a/web/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/web/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2999,6 +2999,76 @@
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>第38号屋</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>3337</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3073,7 +3143,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>33 套</t>
+          <t>34 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -3098,7 +3168,7 @@
       </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>25 套</t>
+          <t>26 套</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3547,15 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr"/>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>第38号屋
+3337呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
       <c r="F11" s="19" t="inlineStr"/>
       <c r="G11" s="19" t="inlineStr"/>
     </row>

--- a/web/files/港岛-大潭及石澳-皇府湾.xlsx
+++ b/web/files/港岛-大潭及石澳-皇府湾.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2546</v>
+        <v>2676</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2507</v>
+        <v>2649</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2507</v>
+        <v>2649</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>47060000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>18771</v>
+        <v>17765</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2507</v>
+        <v>2649</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
         <v>46000000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>18349</v>
+        <v>17365</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2507</v>
+        <v>2649</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2507</v>
+        <v>2649</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2507</v>
+        <v>2649</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2546</v>
+        <v>2676</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>48800000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>19167</v>
+        <v>18236</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2500</v>
+        <v>2612</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2476</v>
+        <v>2583</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2476</v>
+        <v>2583</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2476</v>
+        <v>2583</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2476</v>
+        <v>2583</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2476</v>
+        <v>2583</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2476</v>
+        <v>2583</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2476</v>
+        <v>2583</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2476</v>
+        <v>2583</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2500</v>
+        <v>2612</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3343</v>
+        <v>3483</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3302</v>
+        <v>3447</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3302</v>
+        <v>3447</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3302</v>
+        <v>3447</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>125328000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>37955</v>
+        <v>36359</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3302</v>
+        <v>3447</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3302</v>
+        <v>3447</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3302</v>
+        <v>3447</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3302</v>
+        <v>3447</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3337</v>
+        <v>3474</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>57000000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>17081</v>
+        <v>16408</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3343</v>
+        <v>3483</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3302</v>
+        <v>3447</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3302</v>
+        <v>3447</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3302</v>
+        <v>3447</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3302</v>
+        <v>3447</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3302</v>
+        <v>3447</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>3337</v>
+        <v>3463</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
       <c r="B6" s="16" t="inlineStr">
         <is>
           <t>第1号屋
-2546呎 (4+房)
+2676呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3227,7 +3227,7 @@
       <c r="C6" s="16" t="inlineStr">
         <is>
           <t>第2号屋
-2507呎 (4+房)
+2649呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3236,25 +3236,25 @@
       <c r="D6" s="17" t="inlineStr">
         <is>
           <t>第3号屋
-2507呎 (4+房)
+2649呎 (4+房)
 (98年-05月-14日)
 $4,706万
-$18,771/呎</t>
+$17,765/呎</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
           <t>第5号屋
-2507呎 (4+房)
+2649呎 (4+房)
 (98年-05月-09日)
 $4,600万
-$18,349/呎</t>
+$17,365/呎</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
           <t>第6号屋
-2507呎 (4+房)
+2649呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3263,7 +3263,7 @@
       <c r="G6" s="16" t="inlineStr">
         <is>
           <t>第7号屋
-2507呎 (4+房)
+2649呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3279,7 +3279,7 @@
       <c r="B7" s="16" t="inlineStr">
         <is>
           <t>第8号屋
-2507呎 (4+房)
+2649呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3288,16 +3288,16 @@
       <c r="C7" s="17" t="inlineStr">
         <is>
           <t>第9号屋
-2546呎 (4+房)
+2676呎 (4+房)
 (98年-05月-09日)
 $4,880万
-$19,167/呎</t>
+$18,236/呎</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
           <t>第10号屋
-2500呎 (4+房)
+2612呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3306,7 +3306,7 @@
       <c r="E7" s="16" t="inlineStr">
         <is>
           <t>第11号屋
-2476呎 (4+房)
+2583呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3315,7 +3315,7 @@
       <c r="F7" s="16" t="inlineStr">
         <is>
           <t>第12号屋
-2476呎 (4+房)
+2583呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3324,7 +3324,7 @@
       <c r="G7" s="16" t="inlineStr">
         <is>
           <t>第13号屋
-2476呎 (4+房)
+2583呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3340,7 +3340,7 @@
       <c r="B8" s="16" t="inlineStr">
         <is>
           <t>第15号屋
-2476呎 (4+房)
+2583呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3349,7 +3349,7 @@
       <c r="C8" s="16" t="inlineStr">
         <is>
           <t>第16号屋
-2476呎 (4+房)
+2583呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3358,7 +3358,7 @@
       <c r="D8" s="16" t="inlineStr">
         <is>
           <t>第17号屋
-2476呎 (4+房)
+2583呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3367,7 +3367,7 @@
       <c r="E8" s="16" t="inlineStr">
         <is>
           <t>第18号屋
-2476呎 (4+房)
+2583呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3376,7 +3376,7 @@
       <c r="F8" s="16" t="inlineStr">
         <is>
           <t>第19号屋
-2476呎 (4+房)
+2583呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3385,7 +3385,7 @@
       <c r="G8" s="16" t="inlineStr">
         <is>
           <t>第20号屋
-2500呎 (4+房)
+2612呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3401,7 +3401,7 @@
       <c r="B9" s="18" t="inlineStr">
         <is>
           <t>第21号屋
-3343呎 (4+房)
+3483呎 (4+房)
 (在售)
 招标项目
 -</t>
@@ -3410,7 +3410,7 @@
       <c r="C9" s="16" t="inlineStr">
         <is>
           <t>第22号屋
-3302呎 (4+房)
+3447呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3419,7 +3419,7 @@
       <c r="D9" s="18" t="inlineStr">
         <is>
           <t>第23号屋
-3302呎 (4+房)
+3447呎 (4+房)
 (在售)
 招标项目
 -</t>
@@ -3428,16 +3428,16 @@
       <c r="E9" s="17" t="inlineStr">
         <is>
           <t>第25号屋
-3302呎 (4+房)
+3447呎 (4+房)
 (21年-03月-05日)
 $1.25亿
-$37,955/呎</t>
+$36,359/呎</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
           <t>第26号屋
-3302呎 (4+房)
+3447呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3446,7 +3446,7 @@
       <c r="G9" s="16" t="inlineStr">
         <is>
           <t>第27号屋
-3302呎 (4+房)
+3447呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3462,7 +3462,7 @@
       <c r="B10" s="16" t="inlineStr">
         <is>
           <t>第28号屋
-3302呎 (4+房)
+3447呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3471,7 +3471,7 @@
       <c r="C10" s="18" t="inlineStr">
         <is>
           <t>第29号屋
-3302呎 (4+房)
+3447呎 (4+房)
 (在售)
 招标项目
 -</t>
@@ -3480,16 +3480,16 @@
       <c r="D10" s="17" t="inlineStr">
         <is>
           <t>第30号屋
-3337呎 (4+房)
+3474呎 (4+房)
 (00年-08月-16日)
 $5,700万
-$17,081/呎</t>
+$16,408/呎</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
           <t>第31号屋
-3343呎 (4+房)
+3483呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3498,7 +3498,7 @@
       <c r="F10" s="16" t="inlineStr">
         <is>
           <t>第32号屋
-3302呎 (4+房)
+3447呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3507,7 +3507,7 @@
       <c r="G10" s="16" t="inlineStr">
         <is>
           <t>第33号屋
-3302呎 (4+房)
+3447呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3523,7 +3523,7 @@
       <c r="B11" s="16" t="inlineStr">
         <is>
           <t>第35号屋
-3302呎 (4+房)
+3447呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3532,7 +3532,7 @@
       <c r="C11" s="16" t="inlineStr">
         <is>
           <t>第36号屋
-3302呎 (4+房)
+3447呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3541,7 +3541,7 @@
       <c r="D11" s="16" t="inlineStr">
         <is>
           <t>第37号屋
-3302呎 (4+房)
+3447呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
@@ -3550,7 +3550,7 @@
       <c r="E11" s="16" t="inlineStr">
         <is>
           <t>第38号屋
-3337呎 (4+房)
+3463呎 (4+房)
 (待售)
 暂无价格
 暂无呎价</t>
